--- a/output/review/local-2026-03-21/psa_review.xlsx
+++ b/output/review/local-2026-03-21/psa_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psa" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'psa'!$A$12:$K$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'psa'!$A$12:$L$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,27 +660,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>10508-0</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>50811010000108</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Presence of prostate specific antigen in tissue at point in time by immunohistochemistry (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Presence] in Tissue by Immune stain</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -681,14 +688,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -710,32 +722,32 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>59238-6</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>598871010000108</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of free prostate specific antigen to prostate specific Ag.total in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free/Prostate specific Ag.total in Body fluid</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -767,32 +784,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>59235-2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>598841010000102</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of free prostate specific antigen to prostate specific Ag.total in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free/Prostate specific Ag.total in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -824,32 +846,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>59236-0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>598851010000100</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of free prostate specific antigen to prostate specific Ag.total in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free/Prostate specific Ag.total in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -881,32 +908,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>59237-8</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>598861010000103</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of free prostate specific antigen to prostate specific Ag.total in pleural fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free/Prostate specific Ag.total in Pleural fluid</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -938,32 +970,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>12841-3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>491361010000107</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of free prostate specific antigen to prostate specific Ag.total in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free/Prostate specific Ag.total in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -995,32 +1032,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>48167-1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>562141010000109</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Mass ratio of prostate specific antigen to creatinine in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag/Creatinine [Mass Ratio] in Urine</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1052,32 +1094,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>109229-5</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>717551010000103</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Measurement of free prostate specific antigen in seminal fluid (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Measurement] in Semen</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1109,32 +1156,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>110243-3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>724511010000102</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Measurement of free prostate specific antigen in serum or plasma (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Measurement] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1166,32 +1218,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>109230-3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>717561010000101</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Measurement of prostate specific antigen in seminal fluid (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Measurement] in Semen</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1223,32 +1280,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>110671-5</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>727091010000105</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Measurement of prostate specific antigen in serum or plasma (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Measurement] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1280,24 +1342,24 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>19204-7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>99571010000100</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of free prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Units/volume] in Semen</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1308,9 +1370,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1337,24 +1404,24 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>19201-3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>100121010000105</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of free prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1365,9 +1432,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1394,24 +1466,24 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>19198-1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>189701010000106</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Units/volume] in Semen</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1422,9 +1494,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1451,24 +1528,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>19195-7</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>238361010000109</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Units/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1479,9 +1556,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1508,24 +1590,24 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>59239-4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>160451010000109</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Body fluid</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1536,9 +1618,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1551,12 +1633,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1565,24 +1652,24 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>59231-1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>224431010000103</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1593,9 +1680,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1608,12 +1695,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1622,24 +1714,24 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>59224-6</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>95921010000108</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1650,9 +1742,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1665,12 +1757,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1679,24 +1776,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>59232-9</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>227171010000100</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in pleural fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Pleural fluid</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1707,9 +1804,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1722,12 +1819,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1736,24 +1838,24 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>19205-4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>113051010000107</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Semen</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1764,9 +1866,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1779,12 +1881,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1793,24 +1900,24 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10886-0</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>276781010000103</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1821,9 +1928,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -1836,12 +1943,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1850,24 +1962,24 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>83113-1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>212831010000102</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of free prostate specific antigen in serum or plasma at point in time by immunoassay (observable entity)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Mass/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1878,9 +1990,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -1893,12 +2005,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1907,24 +2024,24 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>47738-0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>51061010000108</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Body fluid</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1935,9 +2052,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -1950,12 +2067,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1964,24 +2086,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>59230-3</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>172721010000104</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1992,9 +2114,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2007,12 +2129,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2021,24 +2148,24 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>100716-0</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>139151010000102</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in dried blood spot at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in DBS</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2049,9 +2176,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2064,12 +2191,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2078,24 +2210,24 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>59223-8</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>190571010000100</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2106,9 +2238,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2121,12 +2253,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2135,24 +2272,24 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>59221-2</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>114091010000101</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in pleural fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Pleural fluid</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2163,9 +2300,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2178,12 +2315,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2192,24 +2334,24 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>19199-9</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>198561010000107</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Semen</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2220,9 +2362,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2235,12 +2377,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2249,24 +2396,24 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>2857-1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>219111010000109</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2277,9 +2424,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2292,12 +2439,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2306,24 +2458,24 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>35741-8</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>235341010000101</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in serum or plasma at point in time by detection limit &lt;= 0.01 ng/mL (observable entity)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Detection limit &lt;= 0.01 ng/mL</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2334,9 +2486,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2349,12 +2501,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2363,24 +2520,24 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>83112-3</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>88701010000106</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in serum or plasma at point in time by immunoassay (observable entity)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2391,9 +2548,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2406,12 +2563,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2420,24 +2582,24 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>34611-4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>161371010000103</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of prostate specific antigen in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Mass/volume] in Urine</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2448,9 +2610,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2463,12 +2625,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2477,24 +2644,24 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>33667-7</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>135211010000105</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of protein-bound prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag.protein bound [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2505,9 +2672,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2520,12 +2687,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2534,24 +2706,24 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>19206-2</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>59841010000103</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of free prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Moles/volume] in Semen</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2562,9 +2734,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2577,12 +2749,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2591,24 +2768,24 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19203-9</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>164181010000104</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of free prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Prostate Specific Ag Free [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2619,9 +2796,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2634,12 +2811,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2648,24 +2830,24 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19200-5</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>222971010000104</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of prostate specific antigen in seminal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Moles/volume] in Semen</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2676,9 +2858,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2691,12 +2873,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2705,24 +2892,24 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>19197-3</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>94521010000100</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of prostate specific antigen in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Prostate specific Ag [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2733,9 +2920,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2748,19 +2935,24 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K50"/>
+  <autoFilter ref="A12:L50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>